--- a/public/templates/examples/A-118-ConfigurationDriftDetectionRecords-EXAMPLE-L.xlsx
+++ b/public/templates/examples/A-118-ConfigurationDriftDetectionRecords-EXAMPLE-L.xlsx
@@ -3,11 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Log!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -15,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="13">
     <font>
       <name val="Aptos"/>
@@ -197,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -262,6 +267,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -885,7 +894,7 @@
       <c r="O10" s="24" t="n"/>
       <c r="P10" s="24" t="n"/>
     </row>
-    <row r="11" ht="27.75" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Entry #</t>
@@ -943,7 +952,7 @@
       <c r="O11" s="24" t="n"/>
       <c r="P11" s="24" t="n"/>
     </row>
-    <row r="12" ht="19.5" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>001</t>
@@ -1001,7 +1010,7 @@
       <c r="O12" s="24" t="n"/>
       <c r="P12" s="24" t="n"/>
     </row>
-    <row r="13" ht="19.5" customHeight="1">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>002</t>
@@ -1059,7 +1068,7 @@
       <c r="O13" s="24" t="n"/>
       <c r="P13" s="24" t="n"/>
     </row>
-    <row r="14" ht="19.5" customHeight="1">
+    <row r="14" ht="34.7" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t>003</t>
@@ -1117,7 +1126,7 @@
       <c r="O14" s="24" t="n"/>
       <c r="P14" s="24" t="n"/>
     </row>
-    <row r="15" ht="19.5" customHeight="1">
+    <row r="15" ht="34.7" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>004</t>
@@ -1437,7 +1446,7 @@
       <c r="O28" s="24" t="n"/>
       <c r="P28" s="24" t="n"/>
     </row>
-    <row r="29" ht="34" customHeight="1">
+    <row r="29" ht="82.2" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Reviewed by (Information Security Analyst)</t>
@@ -1453,10 +1462,8 @@
           <t>(on file)</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
+      <c r="D29" s="29">
+        <v>46042</v>
       </c>
       <c r="E29" s="13" t="n"/>
       <c r="F29" s="13" t="n"/>
@@ -1471,7 +1478,7 @@
       <c r="O29" s="24" t="n"/>
       <c r="P29" s="24" t="n"/>
     </row>
-    <row r="30" ht="51" customHeight="1">
+    <row r="30" ht="66.4" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Approved by (Executive Director)</t>
@@ -1487,10 +1494,8 @@
           <t>(on file)</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
+      <c r="D30" s="29">
+        <v>46042</v>
       </c>
       <c r="E30" s="13" t="n"/>
       <c r="F30" s="13" t="n"/>
@@ -1815,16 +1820,14 @@
       <c r="O45" s="24" t="n"/>
       <c r="P45" s="24" t="n"/>
     </row>
-    <row r="46" ht="17" customHeight="1">
+    <row r="46" ht="34.7" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
+      <c r="B46" s="28">
+        <v>46042</v>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
@@ -1867,8 +1870,8 @@
       <c r="O47" s="24" t="n"/>
       <c r="P47" s="24" t="n"/>
     </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="2" t="n"/>
+    <row r="48">
+      <c r="A48"/>
       <c r="B48" s="24" t="n"/>
       <c r="C48" s="24" t="n"/>
       <c r="D48" s="24" t="n"/>
@@ -2102,7 +2105,7 @@
       <c r="P60" s="24" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="28">
     <mergeCell ref="C3:J3"/>
     <mergeCell ref="A23:J23"/>
     <mergeCell ref="A32:J32"/>
@@ -2118,7 +2121,6 @@
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="A39:J39"/>
     <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A48:J48"/>
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A1:J1"/>
@@ -2134,7 +2136,7 @@
     <mergeCell ref="A33:J33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>